--- a/clean/dic_arg_defun_avp.xlsx
+++ b/clean/dic_arg_defun_avp.xlsx
@@ -467,7 +467,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>grupo_edad_10</t>
+          <t>grupo_edad10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
